--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2019_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2019_los_rios.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:00</t>
+    <t xml:space="preserve">2026-09-24 00:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.28</v>
@@ -704,13 +704,13 @@
         <v>12</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="10">
@@ -727,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +753,7 @@
         <v>0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.42</v>
@@ -796,13 +796,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>12</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>0.08</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.38</v>
